--- a/AAII_Financials/Quarterly/TD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="92">
   <si>
     <t>TD</t>
   </si>
@@ -656,266 +656,278 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="32" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="41" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="34" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45961</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45869</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45777</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45688</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45596</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45504</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45412</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45322</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45230</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45138</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45046</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44957</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44865</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44773</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44592</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44500</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44316</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44227</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44135</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44043</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43951</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43861</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43769</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43677</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43585</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43496</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43404</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43312</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43220</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43131</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>43039</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42947</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42855</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42766</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AQ7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11382400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>10869700</v>
+      </c>
+      <c r="F8" s="3">
         <v>11461100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>10355500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>10351500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>15628700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>8869600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>10533900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>9486500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>9275300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>9502300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>10038300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>9235100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>10384100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>13291200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>10712000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>7967800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>5837200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>5468600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>5510400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>5411800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>5425700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>5714000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>5952200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>6244300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>7438300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>8159800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>8216200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>8824400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>7908400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>8117000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>7262500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>7159800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>6480800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>6182900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>5868800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>5673900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>5527400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>5475200</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AQ8" s="3">
         <v>5282300</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1033,53 +1045,59 @@
       <c r="AO9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>11382400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>10869700</v>
+      </c>
+      <c r="F10" s="3">
         <v>11461100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>10355500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>10351500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>15628700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>8869600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>10533900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>9486500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>9275300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>9502300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>10038300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>9235100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>10384100</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1152,8 +1170,14 @@
       <c r="AO10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1195,8 +1219,10 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1314,8 +1340,14 @@
       <c r="AO12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1433,49 +1465,55 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="F14" s="3">
         <v>147400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>135600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>240600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>118000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3">
         <v>196600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>79600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>120100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>217500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>1443600</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1552,127 +1590,139 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>421300</v>
+      </c>
+      <c r="E15" s="3">
+        <v>412100</v>
+      </c>
+      <c r="F15" s="3">
         <v>402500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>162300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>381500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>386400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>367600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>162500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>356200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>358000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>373000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>158000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>377100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>353200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>-104500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>-107100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>-107200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>-106900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>-116300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>-132600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>-128900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>-129900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>-135200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>-158700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>-155600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>-160900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>-158600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>-164500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>-161700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>-153200</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>-150100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AI15" s="3">
         <v>-157700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AJ15" s="3">
         <v>-140000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AK15" s="3">
         <v>-162600</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AL15" s="3">
         <v>-145900</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AM15" s="3">
         <v>-138400</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AN15" s="3">
         <v>-128700</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AO15" s="3">
         <v>-134400</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AP15" s="3">
         <v>-130600</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AQ15" s="3">
         <v>-139800</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,246 +1761,260 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7054800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>7023800</v>
+      </c>
+      <c r="F17" s="3">
         <v>7348100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>7151500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>6901300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>6657200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>6487900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>7347000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>8975400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>6778200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>6667200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>6066800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>6515100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>7365200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>8106800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>5601200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>3021700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1220600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>939300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>780700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>937000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>761400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1421400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1774000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>3244400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>5097300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>3934700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>4096400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>4373200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>3875300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>4260200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>3566600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>3325100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>2835800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>2657600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>2332400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>2129900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>1986600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>2012000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AQ17" s="3">
         <v>1806900</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4327600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>3845800</v>
+      </c>
+      <c r="F18" s="3">
         <v>4113100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>3204000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>3450300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>8971500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>2381700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>3186900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>511100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>2497100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>2835100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>3971500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>2720100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>3018900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>5184400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>5110800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>4946100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>4616500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>4529300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>4729600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>4474800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>4664300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>4292700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>4178200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>2999900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>2341000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>4225100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>4119800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>4451200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>4033100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>3856800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>3695900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>3834700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>3645000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>3525300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>3536500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>3543900</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>3540800</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>3463200</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AQ18" s="3">
         <v>3475500</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1992,246 +2056,260 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>166800</v>
+      </c>
+      <c r="E20" s="3">
+        <v>157900</v>
+      </c>
+      <c r="F20" s="3">
         <v>153300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>141300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>145200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>86800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-30400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-1400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-12300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-18900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>32900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>20900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-5300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-52400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-3539200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>484600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-2249500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-1264300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-1267900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-1420700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-1291900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-1334300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-1338000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-660800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-1186800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-1149300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-1522200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-1624100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-1335600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-1200900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-1862200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-1213600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>-1139700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-986900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>-1109600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>-1118500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>-1008400</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>-1505700</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>-1146200</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AQ20" s="3">
         <v>-1352100</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4582000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>4100000</v>
+      </c>
+      <c r="F21" s="3">
         <v>4362300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>3225000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>3686500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>9271100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>2779600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>3350900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>879600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>2874000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>3175100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>4108700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>3102500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>3424500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>1962500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>5932800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>3014300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>3670700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>3577600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>3660700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>3530400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>3737800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>3389400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>4004900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>2198700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>1591300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>3090000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>2789700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>3401600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>3097000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>2255600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>2748300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>2947900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>2926100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>2663500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>2665000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>2786300</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>2280900</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>2561300</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AQ21" s="3">
         <v>2392300</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2271,11 +2349,11 @@
       <c r="O22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2349,246 +2427,264 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4167900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3692300</v>
+      </c>
+      <c r="F23" s="3">
         <v>3812300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>2927100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>3064400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>8766700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>2412100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>2991700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>443800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>2396000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>2584700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>2507100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>2725400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>3071300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>1645200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>5595400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>2696600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>3352200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>3261400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>3308900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>3183000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>3330100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>2954600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>3517300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>1813100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>1191700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>2702900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>2495700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>3115600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>2832200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>1994600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>2482400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>2695000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>2658100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>2415700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>2417900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>2535500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>2035000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>2317000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AQ23" s="3">
         <v>2123400</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>878200</v>
+      </c>
+      <c r="E24" s="3">
+        <v>569300</v>
+      </c>
+      <c r="F24" s="3">
         <v>831600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>586600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>653900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>712800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>482300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>383200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>574800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>530400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>473900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>443500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>535200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>633400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>691200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>945200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>519500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>728500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>715400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>674100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>683000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>722300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>621000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-154900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>341200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>196300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>517300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>503700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>674000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>595100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>387200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>502100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>530700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>561600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>774000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>476300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>565600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>197400</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>457900</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AQ24" s="3">
         <v>426400</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2706,246 +2802,264 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3289700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>3122900</v>
+      </c>
+      <c r="F26" s="3">
         <v>2980700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>2340600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>2410500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>8053900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1929800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>2608500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-131000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1865500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>2110800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>2063500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>2190200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>2437900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>954000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>4650200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>2177100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>2623800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>2546000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>2634800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>2500000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>2607700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>2333700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>3672200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>1471900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>995400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>2185600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>1992100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>2441600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>2237100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>1607400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>1980200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>2164300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>2096500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>1641700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>1941600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>1969900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>1837600</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>1859100</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AQ26" s="3">
         <v>1697000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3222700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2974500</v>
+      </c>
+      <c r="F27" s="3">
         <v>2906200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>2204300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>2346900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>7909100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1870400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>2470000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-181000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1727300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>2055500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1922400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>2133900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>2283000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1102700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>4783600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>2343300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>2722700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>2682700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>2754100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>2584400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>2725600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>2411800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>3893800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>1671300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>1136000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>2293900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>2173700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>2641400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>2394100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>1795200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>2100900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>2279400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>2142400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>1699000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>1955000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>2004200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>1864500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>1886800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AQ27" s="3">
         <v>1713900</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3063,8 +3177,14 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3182,8 +3302,14 @@
       <c r="AO29" s="3">
         <v>0</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3301,8 +3427,14 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3420,246 +3552,264 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-166800</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-157900</v>
+      </c>
+      <c r="F32" s="3">
         <v>-153300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-141300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-145200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-86800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>30400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>1400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>12300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>18900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-32900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-20900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>5300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>52400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>3539200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-484600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>2249500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>1264300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>1267900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>1420700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>1291900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>1334300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>1338000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>660800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>1186800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>1149300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>1522200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>1624100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>1335600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>1200900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>1862200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>1213600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>1139700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>986900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>1109600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>1118500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>1008400</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>1505700</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>1146200</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AQ32" s="3">
         <v>1352100</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3289700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>3122900</v>
+      </c>
+      <c r="F33" s="3">
         <v>2980700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>2340600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>2410500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>8053900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1929800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>2608500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-131000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1865500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>2110800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>2063500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>2190200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>2437900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>1102700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>4783600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>2343300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>2722700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>2682700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>2754100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>2584400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>2725600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>2411800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>3893800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>1671300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>1136000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>2293900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>2173700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>2641400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>2394100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>1795200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>2100900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>2279400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>2142400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>1699000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>1955000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>2004200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>1864500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>1886800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AQ33" s="3">
         <v>1713900</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3777,251 +3927,269 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3289700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>3122900</v>
+      </c>
+      <c r="F35" s="3">
         <v>2980700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>2340600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>2410500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>8053900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1929800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>2608500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-131000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1865500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>2110800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>2063500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>2190200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>2437900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>1102700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>4783600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>2343300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>2722700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>2682700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>2754100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>2584400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>2725600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>2411800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>3893800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>1671300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>1136000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>2293900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>2173700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>2641400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>2394100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>1795200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>2100900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>2279400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>2142400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>1699000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>1955000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>2004200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>1864500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>1886800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AQ35" s="3">
         <v>1713900</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45961</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45869</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45777</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45688</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45596</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45504</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45412</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45322</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45230</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45138</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45046</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44957</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44865</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44773</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44592</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44500</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44316</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44227</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44135</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44043</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43951</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43861</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43769</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43677</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43585</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43496</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43404</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43312</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43220</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43131</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>43039</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42947</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42855</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42766</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AQ38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4063,8 +4231,10 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4106,291 +4276,305 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4855800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4303500</v>
+      </c>
+      <c r="F41" s="3">
         <v>4635000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>5360400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>3986400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3981000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>4527000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>4619300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>5244900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>4589600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>4733600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>4839200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>5640800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>5068900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>5143900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>6235300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>4193000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>4095200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>5089800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>4393300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>4308900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>4293400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>4692900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>4941000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>4147500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>4158400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>3982600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>3791500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>4155200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>3856000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>3372600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>3440900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>4171200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>3159500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>2899400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>2955300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>3060900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>4049300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>2879300</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AQ41" s="3">
         <v>3001500</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>446680700</v>
+      </c>
+      <c r="E42" s="3">
+        <v>463779600</v>
+      </c>
+      <c r="F42" s="3">
         <v>477708100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>466859100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>445027600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>460272000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>441185400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>451291000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>394686300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>392337000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>369309900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>388429500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>388354200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>391658500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>550838500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>553925400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>528193100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>532135000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>506129100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>492270600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>478246200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>471057300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>487331400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>481847800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>472006400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>440428000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>307029900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>297406700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>312002200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>262624900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>249415500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>239734300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>239473000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AK42" s="3">
         <v>248446300</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AL42" s="3">
         <v>237815300</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AM42" s="3">
         <v>182957300</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AN42" s="3">
         <v>173342100</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AO42" s="3">
         <v>180308200</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AP42" s="3">
         <v>165984500</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AQ42" s="3">
         <v>166161200</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>26835000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>31116900</v>
+      </c>
+      <c r="F43" s="3">
         <v>37342000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>28870800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>27115900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>36130600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>31563400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>24489400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>35512200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>37148600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>37622700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>35326300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>30102400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>33129300</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4463,53 +4647,59 @@
       <c r="AO43" s="3">
         <v>0</v>
       </c>
+      <c r="AP43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E44" s="3">
+      <c r="D44" s="3">
+        <v>63400</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3">
         <v>72100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>114900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>123700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>120200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>90400</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M44" s="3">
         <v>55300</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O44" s="3">
         <v>42500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>40300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>41300</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
@@ -4582,53 +4772,59 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8787700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>9407700</v>
+      </c>
+      <c r="F45" s="3">
         <v>9827400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>8116300</v>
       </c>
-      <c r="F45" s="3">
-        <v>5077500</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
+        <v>12309700</v>
+      </c>
+      <c r="I45" s="3">
         <v>9755300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>7889800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>9563000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>8536700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>11001900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>18142000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>21052200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>23087900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>22907400</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4701,53 +4897,59 @@
       <c r="AO45" s="3">
         <v>0</v>
       </c>
+      <c r="AP45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>488678200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>510022600</v>
+      </c>
+      <c r="F46" s="3">
         <v>530860100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>510573900</v>
       </c>
-      <c r="F46" s="3">
-        <v>482865000</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
+        <v>490097200</v>
+      </c>
+      <c r="I46" s="3">
         <v>511475400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>486906100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>491340500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>445278800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>446301700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>431068300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>450742300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>448655600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>454148300</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4820,365 +5022,389 @@
       <c r="AO46" s="3">
         <v>0</v>
       </c>
+      <c r="AP46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>279844900</v>
+      </c>
+      <c r="E47" s="3">
+        <v>284154700</v>
+      </c>
+      <c r="F47" s="3">
         <v>281285200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>275295800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>275173200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>276455000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>264760100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>278715500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>271947300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>281874300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>293783500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>285143400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>297712500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>311280100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>6152400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>5894200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>7023400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>7070900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>8132300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>8231100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>8319300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>8031900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>8815100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>9333100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>7677100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>7987900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>7423400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>7263400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>7551000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>6949200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>6681300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>6136900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>6154100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>5950100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AL47" s="3">
         <v>5585300</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AM47" s="3">
         <v>5792900</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AN47" s="3">
         <v>4996600</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AO47" s="3">
         <v>5593500</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AP47" s="3">
         <v>5287700</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AQ47" s="3">
         <v>5447500</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7275800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>7330900</v>
+      </c>
+      <c r="F48" s="3">
         <v>7309700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>7230000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>7117300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>7027700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>7013700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>7059200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>6929600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>6924500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>7118700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>6792500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>6987200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>6905000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>6773700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>6850300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>6723300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>6713900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>6753200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>6800700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>6854100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>6953700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>7313400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>7770700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>7378900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>7739000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>7555300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>4298300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>4529100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>4234000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>4120800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>3868900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>3923500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>3904700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>3797000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>3954000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>3835700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>4195300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>4113900</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AQ48" s="3">
         <v>4211400</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>16268100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>16223700</v>
+      </c>
+      <c r="F49" s="3">
         <v>16152200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>15976400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>15947800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>15827000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>15713300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>15712200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>15690000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>15683200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>15619400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>15388700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>15610300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>15410300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>14446900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>14545300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>13984600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>13765200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>13643800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>13596300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>13689600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>13435900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>13920200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>14775500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>14919600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>15851700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>15284100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>15187200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>16225300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>15284800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>15079200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>13803500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>14184800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>14060600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>13454600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>13971800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>13556500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>15101900</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AP49" s="3">
         <v>14506500</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AQ49" s="3">
         <v>14827600</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5296,8 +5522,14 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5415,127 +5647,139 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1481200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1456800</v>
+      </c>
+      <c r="F52" s="3">
         <v>1425100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>1460700</v>
       </c>
-      <c r="F52" s="3">
-        <v>8752500</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
+        <v>1520300</v>
+      </c>
+      <c r="I52" s="3">
         <v>1510300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>1496600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1600300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1452900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1204200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1326700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1408300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>2672900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>2589800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>3257300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>2622800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>3061600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>2568500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>2338100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>2149600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1755600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>1655600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1680400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>1880600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>1509500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>1284300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>1425700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>1412800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>1581800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>1652000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>1751300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>2125600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>2099500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>2013000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>1760100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>1868000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>1847900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>1847600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>1771500</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AQ52" s="3">
         <v>1609400</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5653,127 +5897,139 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1505386100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1531791300</v>
+      </c>
+      <c r="F54" s="3">
         <v>1547692800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1494639600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1470545900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1493880500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1446513900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1479548600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1424121000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1430928400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1428287800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1407709100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1434590700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1420572100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1419429100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1397417700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1360340900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1326993900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1293051300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1280496500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1261549100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1253228900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1303188900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1315450700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1301221900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1313973500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1144154600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1103459200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1165181700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1044328600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1018091600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>970060700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>972984100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>966458900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>938684000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>951840900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>894824000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>961762500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>911799100</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AQ54" s="3">
         <v>904181400</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5815,8 +6071,10 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5858,226 +6116,234 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>966273400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>985382200</v>
+      </c>
+      <c r="F57" s="3">
         <v>994200900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>953614300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>959627200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>959374600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>939044200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>962659500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>931502200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>918966100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>922214100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>915969700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>937268200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>947940100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>22170200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>23396800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>28381600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>25481000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>23768900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>27560000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>22608900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>19369200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>32981500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>32855100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>17609000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>27264800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>26153200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>23677000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>23390800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>19659700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>24690400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>25162400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>15362900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>17388700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>22751200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>28526300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>16802800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>27514900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>22888600</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AQ57" s="3">
         <v>17836800</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>53681400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>54753800</v>
+      </c>
+      <c r="F58" s="3">
         <v>222369300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>218112900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>205165600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>197646600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>186186800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>194348800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>177085900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>192964900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>172888700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>173933000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>177298300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>159262200</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>193311200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>206126200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>222569400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>211067200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>190462400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>200124500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>217373100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>234594100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>225004800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>216535600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>203215500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>210811700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>155529000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>123584600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>96564700</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ58" s="3" t="s">
         <v>5</v>
       </c>
@@ -6087,181 +6353,193 @@
       <c r="AL58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AM58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN58" s="3">
-        <v>0</v>
+      <c r="AM58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>30958000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>31228600</v>
+      </c>
+      <c r="F59" s="3">
         <v>33676400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>33411400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>31688300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>33547100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>34572400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>30355900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>31172900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>33267600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>44734600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>47536900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>53166700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>54379100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>2296700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>3098000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>2611600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>2488600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>2114900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>3135600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>2771100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>2333700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1823100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>2434100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>2204900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1728700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>1654100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>2661800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>2519500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>2068500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>1693600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>3760600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>3897200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>3695400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>3469500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>4385600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>3863900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>4044000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>3443200</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AQ59" s="3">
         <v>4531000</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1078253900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1100377600</v>
+      </c>
+      <c r="F60" s="3">
         <v>1278708500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1233252900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1218241300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1220384700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1184531300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1214305700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1165209600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1174874900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1171250300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1166445600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1189344800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1186764300</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6334,246 +6612,264 @@
       <c r="AO60" s="3">
         <v>0</v>
       </c>
+      <c r="AP60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>326537700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>329242900</v>
+      </c>
+      <c r="F61" s="3">
         <v>167254000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>161238200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>153815500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>160619300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>158435300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>159033400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>154299100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>153258100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>153069400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>141138200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>138894300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>128977000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>44575100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>43141900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>46707100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>46573700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>44557700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>12372600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>12500000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>12657200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>12926800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>13471400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>13788000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>15481200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>12841100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>8362000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>8784600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>6903700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>6846000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>6351300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>5286800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>5744500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>5595000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>7090800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>7229300</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>6516100</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>6448500</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AQ61" s="3">
         <v>8366800</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8893900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>9645800</v>
+      </c>
+      <c r="F62" s="3">
         <v>7931200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>7738100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>6717000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>20428100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>20117300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>22363100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>22681000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>20219700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>18798300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>18391100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>19565800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>18043500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>3333100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>2071100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>2208100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>2202800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>2302400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>2325900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>2608900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>2631800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>3327800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>3952000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>4283200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>3726600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>3295600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>3172500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>3462100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>3036200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>2897600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>1218700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>1159300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>1108900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>1096200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>888600</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>959300</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>1046300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>1004100</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AQ62" s="3">
         <v>1052500</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6691,8 +6987,14 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6810,8 +7112,14 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6929,127 +7237,139 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1414846700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1440463000</v>
+      </c>
+      <c r="F66" s="3">
         <v>1455098400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1403424500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1379940000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1402630600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1364289600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1396907800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1343346600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1349451400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1344248800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1327017500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1348941400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1334949200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1337099600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1316246200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1284526500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1254720400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1218913000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1206557300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1187544000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1182261400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1231538000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1242237400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1230333800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1240701700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1074440600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1035081300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>1093566700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>978972400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>955220400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>912618000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>915249600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>909495300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>884960900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>896615300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>841333100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>904462500</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>856732400</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AQ66" s="3">
         <v>848435500</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7091,8 +7411,10 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7210,8 +7532,14 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7329,127 +7657,139 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>1998800</v>
+      </c>
+      <c r="E70" s="3">
+        <v>2083400</v>
+      </c>
+      <c r="F70" s="3">
         <v>2093000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="G70" s="3">
         <v>2030900</v>
       </c>
-      <c r="F70" s="3">
+      <c r="H70" s="3">
         <v>2202400</v>
       </c>
-      <c r="G70" s="3">
+      <c r="I70" s="3">
         <v>2440300</v>
       </c>
-      <c r="H70" s="3">
+      <c r="J70" s="3">
         <v>2313900</v>
       </c>
-      <c r="I70" s="3">
+      <c r="K70" s="3">
         <v>2785800</v>
       </c>
-      <c r="J70" s="3">
+      <c r="L70" s="3">
         <v>3777500</v>
       </c>
-      <c r="K70" s="3">
+      <c r="M70" s="3">
         <v>3523000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="N70" s="3">
         <v>3866500</v>
       </c>
-      <c r="M70" s="3">
+      <c r="O70" s="3">
         <v>3697200</v>
       </c>
-      <c r="N70" s="3">
+      <c r="P70" s="3">
         <v>4248900</v>
       </c>
-      <c r="O70" s="3">
+      <c r="Q70" s="3">
         <v>4122100</v>
       </c>
-      <c r="P70" s="3">
+      <c r="R70" s="3">
         <v>8276800</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="S70" s="3">
         <v>8195600</v>
       </c>
-      <c r="R70" s="3">
+      <c r="T70" s="3">
         <v>5419800</v>
       </c>
-      <c r="S70" s="3">
+      <c r="U70" s="3">
         <v>4752500</v>
       </c>
-      <c r="T70" s="3">
+      <c r="V70" s="3">
         <v>4139600</v>
       </c>
-      <c r="U70" s="3">
+      <c r="W70" s="3">
         <v>4214800</v>
       </c>
-      <c r="V70" s="3">
+      <c r="X70" s="3">
         <v>4959300</v>
       </c>
-      <c r="W70" s="3">
+      <c r="Y70" s="3">
         <v>3713000</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Z70" s="3">
         <v>4239400</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="AA70" s="3">
         <v>4328400</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AB70" s="3">
         <v>4442700</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AC70" s="3">
         <v>4550900</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AD70" s="3">
         <v>4547800</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AE70" s="3">
         <v>4517400</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AF70" s="3">
         <v>4805200</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AG70" s="3">
         <v>4113900</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AH70" s="3">
         <v>4116200</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AI70" s="3">
         <v>3628400</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AJ70" s="3">
         <v>3648800</v>
       </c>
-      <c r="AI70" s="3">
+      <c r="AK70" s="3">
         <v>3835500</v>
       </c>
-      <c r="AJ70" s="3">
+      <c r="AL70" s="3">
         <v>3528300</v>
       </c>
-      <c r="AK70" s="3">
+      <c r="AM70" s="3">
         <v>3529800</v>
       </c>
-      <c r="AL70" s="3">
+      <c r="AN70" s="3">
         <v>3529000</v>
       </c>
-      <c r="AM70" s="3">
+      <c r="AO70" s="3">
         <v>3374800</v>
       </c>
-      <c r="AN70" s="3">
+      <c r="AP70" s="3">
         <v>3376400</v>
       </c>
-      <c r="AO70" s="3">
+      <c r="AQ70" s="3">
         <v>3376400</v>
       </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7567,127 +7907,139 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>56229000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>57518300</v>
+      </c>
+      <c r="F72" s="3">
         <v>57691300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>55887800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>56901600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>56910500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>49552600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>50826000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>50180600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>52316600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>54075400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>52566100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>56757200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>55193900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>54104800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>53708200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>51056800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>48743100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>47707100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>47365900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>45308800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>44327000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>42072200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>41279700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>38281400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>39018600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>39345900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>38591300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>40472600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>36936000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>35919800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>33533100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>33290600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>32643200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>31066300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>30132300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>29376200</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>28867800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>28678000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AQ72" s="3">
         <v>27235300</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7805,8 +8157,14 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7924,8 +8282,14 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8043,127 +8407,139 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>88540600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>89244900</v>
+      </c>
+      <c r="F76" s="3">
         <v>90501400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>89184200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>88403500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>88809700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>79910300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>79855000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>76996800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>77954000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>80172500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>76994400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>81400500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>81500800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>74052700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>72975800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>70394700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>67521100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>69998700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>69724400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>69045900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>67254500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>67411500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>68884900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>66445500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>68720900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>65166200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>63860400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>66809800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>61242300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>58755000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>53814300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>54085700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>53128200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>50194700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>51695800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>49961800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>53925100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>51690400</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AQ76" s="3">
         <v>52369500</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8281,251 +8657,269 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45961</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45869</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45777</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45688</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45596</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45504</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45412</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45322</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45230</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45138</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45046</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44957</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44865</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44773</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44592</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44500</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44316</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44227</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44135</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44043</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43951</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43861</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43769</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43677</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43585</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43496</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43404</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43312</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43220</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43131</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>43039</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42947</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42855</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42766</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AQ80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3289700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>3122900</v>
+      </c>
+      <c r="F81" s="3">
         <v>2980700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>2340600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>2410500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>8053900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1929800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>2608500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-131000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1865500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>2110800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>2063500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>2190200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>2437900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>1102700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>4783600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>2343300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>2722700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>2682700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>2754100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>2584400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>2725600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>2411800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>3893800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>1671300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>1136000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>2293900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>2173700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>2641400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>2394100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>1795200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>2100900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>2279400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>2142400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>1699000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>1955000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>2004200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>1864500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>1886800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AQ81" s="3">
         <v>1713900</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8567,127 +8961,135 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>236300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>246100</v>
+      </c>
+      <c r="F83" s="3">
         <v>238400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>-3600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>230900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>235700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>234700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>10800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>244000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>227900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>216700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>-24900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>222400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>227100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>317300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>337400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>317800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>318400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>316200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>351900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>347400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>407700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>434700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>487600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>385600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>399600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>387000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>293900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>286000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>264800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>261000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>266000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>252900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>268000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>247800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>247100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>250800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>245800</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>244300</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AQ83" s="3">
         <v>268900</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8805,8 +9207,14 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8924,8 +9332,14 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9043,8 +9457,14 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9162,8 +9582,14 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9281,127 +9707,139 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-19482200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>11000400</v>
+      </c>
+      <c r="F89" s="3">
         <v>22190200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-17393600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-10988100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>23818600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-47585500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>23805500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-19912000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-12967800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2115300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-19319200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-3173200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-16312800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>3723200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1888200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>13973600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-8213800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>20899400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>10463000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>7198500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-14544200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>34281300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>17385100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>46377100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>108296100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>8374100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>621400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>3688400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-1284100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-2545800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>1341500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>5841700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>-4625100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>1660300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>13551300</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>-1094700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>6580700</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>7348900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AQ89" s="3">
         <v>838900</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9443,127 +9881,135 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-521100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-458400</v>
+      </c>
+      <c r="F91" s="3">
         <v>-391500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-454600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-415500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-315500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-343400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-511700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-411200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-309200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-352000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-398900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-390800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-275100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-403000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-461000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-254000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-406000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-333000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-358000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-286000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-361900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-720600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-144100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-327400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-166400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-168400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-93700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-224800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-133200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-189700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-131700</v>
       </c>
-      <c r="AI91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK91" s="3">
+      <c r="AK91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM91" s="3">
         <v>-227000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>106400</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-385700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-32300</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AQ91" s="3">
         <v>88300</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9681,8 +10127,14 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9800,127 +10252,139 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>7019200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-2844500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-8082400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>10666600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>18878600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-3479500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>34492300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-57499100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>10797600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-2662300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>17525400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-5834900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>27075200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>39831600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-3902100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-1085100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-13380200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>7771000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-16713200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-12437000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-4130400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>13691200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-30887400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-14658900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-44200600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-108946900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-6721600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>706400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-3608000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>2982300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>3909100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-2462800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-2171800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>5460000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>424200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>16454500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-22394000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-3628400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>-4786100</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AQ94" s="3">
         <v>4564800</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9962,26 +10426,28 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>5</v>
+      <c r="D96" s="3">
+        <v>1311600</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F96" s="3">
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3">
         <v>1299200</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I96" s="3" t="s">
         <v>5</v>
       </c>
@@ -10003,86 +10469,92 @@
       <c r="O96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R96" s="3">
         <v>-827400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-1571200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-1154300</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-2142500</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-2051800</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-1050500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-1040700</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-1060300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-696100</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-1110800</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-1049600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-1043200</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-1091900</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-1011500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-914500</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AI96" s="3">
         <v>-857500</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AJ96" s="3">
         <v>-897300</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AK96" s="3">
         <v>-902600</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AL96" s="3">
         <v>-791100</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AM96" s="3">
         <v>-798500</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AN96" s="3">
         <v>-796300</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AO96" s="3">
         <v>-827400</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AP96" s="3">
         <v>-761300</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AQ96" s="3">
         <v>-751300</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10200,8 +10672,14 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10319,8 +10797,14 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10438,361 +10922,385 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>13009800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-8468100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-14876000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>8113400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-7891900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-20939800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>13044900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>33085800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>9783300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>15523900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-15581300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>24470800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-23385100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-23664000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-893600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>1111400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-557900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-578000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-3485300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-2095600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>1157800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-1612800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-1217900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-2014000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-1995600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>793700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-1499400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-1440100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-39000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-1260200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-1632800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>515200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-2681400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-685000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-2057000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>5833100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>3351200</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>10220500</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>5342300</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AQ100" s="3">
         <v>-5949900</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-159900</v>
+      </c>
+      <c r="F101" s="3">
         <v>127800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>28000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>9400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>88000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-118800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>180000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-101900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>61200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-83200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>187000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-5500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>28100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-81700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>185800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-5200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>26200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>77100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-39300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>40700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-135900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-120100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-13800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-92000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>128000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>11800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-39000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>45400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-3100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>20300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>23300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>76800</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>-83400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>58000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>-159300</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>90700</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AP101" s="3">
         <v>-58400</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AQ101" s="3">
         <v>39900</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>680000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-315200</v>
+      </c>
+      <c r="F102" s="3">
         <v>-903100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1423600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>11600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-760600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>79500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-579800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>678300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-18200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-290000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-503300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>415100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-84100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-1154200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>2100300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>30300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-994500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>777900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>84400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>73300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-399500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-146400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>793500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>86600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>175900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>164900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-116200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>2500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>483400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-272500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-585700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>1011700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>226600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>-55800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>-105700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>-861800</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>1170000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>-122100</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AQ102" s="3">
         <v>241200</v>
       </c>
     </row>
